--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -764,7 +764,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm đơn vị rời rạc hoặc từng đoạn mà mô hình xử lý sau bước tiền xử lý.</t>
+          <t>Văn bản (x1) biểu diễn bằng mảnh từ hoặc mã định danh token (r1); Hình ảnh (x2) biểu diễn bằng mảnh ảnh (image patches) hoặc token hình ảnh (r2); Âm thanh (x3) biểu diễn bằng khung/đoạn âm thanh được mã hóa thành token (r3).</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ kết luận trong đúng phạm vi và đúng loại cơ chế đã được đo.</t>
+          <t>Các thí nghiệm probe và can thiệp trên mô hình Othello chỉ chứng minh mô hình học được biểu diễn nội tại về trạng thái bàn cờ của trò chơi đó. Kết luận 'Mô hình đã có hiểu biết có ý thức và world model tổng quát cho mọi lĩnh vực' vượt quá bằng chứng thu được nhiều nhất.</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cùng danh tính token nhưng vai trò có thể thay đổi theo vị trí trong câu.</t>
+          <t>Kiến trúc Transformer xử lý các token song song và có tính bất biến với thứ tự (permutation invariant); positional encoding bổ sung thông tin vị trí vào vector biểu diễn để attention phân biệt được trật tự từ ('chó cắn mèo' khác 'mèo cắn chó').</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Attention cần nhận biểu diễn đã mang cả danh tính token và vị trí.</t>
+          <t>Luồng đầu vào Transformer trước khối attention gồm: tách văn bản thành token IDs (o4) -&gt; tra token embedding từ token IDs (o2) -&gt; cộng hoặc kết hợp thông tin vị trí positional encoding (o1) -&gt; đưa biểu diễn vào khối attention (o3).</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ kết luận trong đúng head, đúng tầng và đúng ba token được quan sát.</t>
+          <t>Trọng số attention 0,62 tới `river` cho thấy trong head và tầng cụ thể này, biểu diễn của token `bank` nhận được đóng góp lớn nhất từ token `river` trong số ba token được quan sát.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -627,10 +627,18 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So từng thành phần: mẫu thử, chỉ số đo, mức tác động và phạm vi kết luận.
-Phân tích theo nguyên lý thiết kế: So từng thành phần: mẫu thử, chỉ số đo, mức tác động và phạm vi kết luận.</t>
+- Chỉ ra 2 lỗi vượt quá bằng chứng (1.5 điểm): Nêu đúng sai lệch về chỉ số (8% giảm thời gian vs 30% năng suất) và phóng đại phạm vi (40 người vs mọi người dùng).
+- Viết lại nhận định trung thực (1.5 điểm): Viết lại câu chuẩn xác, giữ nguyên cỡ mẫu 40 người và số liệu giảm thời gian trung vị 8%.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Hai chỗ kết luận vượt quá bằng chứng:
+1. Phóng đại chỉ số và mức tác động: Nguồn A chỉ ghi 'thời gian hoàn thành trung vị giảm 8%', nhưng LLM bịa ra kết luận 'tăng năng suất 30%'.
+2. Khái quát hóa quá mức phạm vi đối tượng: Nguồn A chỉ thử nghiệm trên cỡ mẫu nhỏ gồm '40 người', nhưng LLM lại khẳng định tuyệt đối cho 'mọi nhóm người dùng'.
+- Viết lại nhận định phù hợp với nguồn:
+"Theo nghiên cứu thử nghiệm trên nhóm 40 người tham gia, kết quả ghi nhận thời gian hoàn thành công việc trung vị giảm 8%."
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Đây là hai dạng ảo giác suy diễn kinh điển trong LLM: Phóng đại số liệu (metric extrapolation hallucination) và Khái quát hóa sai phạm vi (scope overgeneralization). Trong thiết kế AI sản phẩm, mọi khẳng định định lượng phải tuân thủ nghiêm ngặt nguyên tắc trung thực với ngữ cảnh (Faithfulness/Factuality to Context).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Ji, Z., et al. (2023). Survey of Hallucination in Natural Language Generation. ACM Computing Surveys, 55(12), 1-38. https://arxiv.org/abs/2202.03629; Ragas Evaluation Metric - Faithfulness.</t>
         </is>
       </c>
     </row>
@@ -711,10 +719,17 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng dùng nguồn này để âm thầm sửa nguồn kia; hãy giữ nguồn gốc từng số và tìm khác biệt về phiên bản hoặc thời điểm.
-Phân tích theo nguyên lý thiết kế: Đừng dùng nguồn này để âm thầm sửa nguồn kia; hãy giữ nguồn gốc từng số và tìm khác biệt về phiên bản hoặc thời điểm.</t>
+- Trình bày câu trả lời minh bạch mâu thuẫn (1.5 điểm): Nêu rõ cả hai số liệu (100 và 60 req/min) từ hai tài liệu mà không tự ý thiên vị một số.
+- Đề xuất bước xác minh kỹ thuật tiếp theo (1.5 điểm): Đưa ra hành động cụ thể như đối chiếu phiên bản SDK, kiểm tra thực nghiệm hoặc hỏi quản trị viên.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Câu trả lời không âm thầm chọn một con số:
+"Hiện có sự không nhất quán giữa hai tài liệu được cung cấp: Tài liệu chính thức ghi nhận giới hạn là 100 yêu cầu/phút, trong khi tài liệu SDK (phiên bản cũ) ghi nhận mức 60 yêu cầu/phút. Do sự khác biệt về nguồn và phiên bản tài liệu, hệ thống không tự ý áp dụng một con số duy nhất."
+- Bước tiếp theo cần thực hiện:
+Tiến hành kiểm tra số hiệu phiên bản của SDK hiện hành đang chạy trong dự án; thực hiện gọi thử nghiệm API (probe request) hoặc liên hệ đội ngũ quản trị dịch vụ/kênh hỗ trợ chính thức để xác nhận ngưỡng rate limit có hiệu lực thực tế cho môi trường hiện tại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc xử lý xung đột thông tin (Conflict Transparency Principle) quy định hệ thống AI không được phép tự ý đưa ra giả định ngầm định khi dữ liệu đầu vào mâu thuẫn. Việc chỉ ra sự khác biệt và hướng dẫn quy trình xác minh phiên bản giúp bảo vệ hệ thống khỏi các lỗi giới hạn tải nghiêm trọng khi vận hành thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Addressing Discrepancies and Failure Handling (https://sre.google/sre-book/); AWS Well-Architected Framework - Reliability Pillar.</t>
         </is>
       </c>
     </row>
@@ -798,10 +813,15 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách hai tầng: dữ liệu ban đầu được mã hóa thế nào và mô hình liên kết các biểu diễn sau mã hóa ra sao.
-Phân tích theo nguyên lý thiết kế: Tách hai tầng: dữ liệu ban đầu được mã hóa thế nào và mô hình liên kết các biểu diễn sau mã hóa ra sao.</t>
+- Nêu phần dùng chung của context + attention (1.5 điểm): Chỉ ra không gian embedding chung và các khối Transformer self-attention sau khi qua projector.
+- Nêu phần khác biệt bản chất (1.5 điểm): Phân biệt rõ tính tuần tự 1D của văn bản rời rạc với cấu trúc không gian 2D liên tục của patch ảnh biểu đồ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phần trong cơ chế `context + attention` có thể dùng chung: Sau khi qua các bộ chiếu (projector/linear projection), các biểu diễn của văn bản và hình ảnh đều được chuyển đổi thành các chuỗi vector liên tục có cùng số chiều không gian ẩn ($d_{model}$). Do đó, các tầng Transformer Backbone (cơ chế Self-Attention đa đầu, Feed-Forward Network, Residual Connection và LayerNorm) hoàn toàn có thể dùng chung để tính toán ma trận tương tác giữa token chữ và token ảnh.
+2. Phần không nên coi là giống hệt giữa hai loại dữ liệu: Khâu mã hóa và bản chất cấu trúc ban đầu. Văn bản là chuỗi token 1 chiều rời rạc có tính ngữ nghĩa tuần tự (1D sequence via BPE). Ngược lại, biểu đồ là dữ liệu không gian 2D liên tục (2D image patches) chứa cấu trúc hình học, tọa độ, màu sắc và mật độ pixel được trích xuất qua Vision Encoder (ViT), đòi hỏi cơ chế positional encoding 2 chiều và các phép chiếu đặc trưng riêng biệt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Kiến trúc đa phương thức (Multimodal Transformer như CLIP, LLaVA, GPT-4V) áp dụng nguyên lý 'Unified Representation': tách biệt khâu xử lý thô riêng biệt theo phương thức (Modality-specific encoder) và hợp nhất ở tầng Transformer biểu diễn chung (Unified Attention Space). Đồng nhất hóa quá sớm bản chất dữ liệu sẽ phá vỡ tính toàn vẹn về không gian 2D của biểu đồ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Radford, A., et al. (2021). Learning Transferable Visual Models From Natural Language Supervision (CLIP). ICML 2021. https://arxiv.org/abs/2103.00020; Liu, H., et al. (2023). Visual Instruction Tuning (LLaVA).</t>
         </is>
       </c>
     </row>
@@ -926,10 +946,15 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Probe trả lời câu hỏi “có đọc được không”; can thiệp trả lời một câu hỏi khác về quan hệ nhân quả.
-Phân tích theo nguyên lý thiết kế: Probe trả lời câu hỏi “có đọc được không”; can thiệp trả lời một câu hỏi khác về quan hệ nhân quả.</t>
+- Kết luận được hỗ trợ (1.5 điểm): Nêu rõ mô hình có mã hóa thông tin/tương quan về biến Z trong trạng thái ẩn.
+- Kết luận chưa được hỗ trợ (1.5 điểm): Giải thích rõ biến Z không có vai trò nhân quả (causality) vì can thiệp không làm thay đổi đầu ra (chỉ là tương quan bề mặt).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Kết luận ĐƯỢC hỗ trợ: Trạng thái ẩn (`hidden state`) của mô hình CÓ CHỨA tương quan thông tin (statistical correlation / linear decodability) về biến Z với độ chính xác cao. Điều này chứng minh quá trình xử lý nội tại của mô hình đã trích xuất và mã hóa biểu diễn của biến Z.
+- Kết luận CHƯA ĐƯỢC hỗ trợ: Biến Z đóng vai trò nhân quả (causal mechanism / causally efficacious) trong việc tạo ra kết quả đầu ra của mô hình. Việc can thiệp (ablation/intervention) vào hướng biểu diễn của Z mà không làm thay đổi đầu ra cho thấy biểu diễn Z có thể chỉ là một biến phụ ngẫu nhiên (epiphenomenon) hoặc thông tin dư thừa mà các tầng tính toán phía sau không hề sử dụng để đưa ra quyết định.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Thí nghiệm Probing trong diễn giải mô hình (Mechanistic Interpretability) chỉ chứng minh sự tồn tại của thông tin (Correlation is not Causation). Để chứng minh một khái niệm trong mạng nơ-ron thực sự quyết định hành vi đầu ra, bắt buộc phải có thử nghiệm can thiệp (Interchange Intervention / Causal Mediation Analysis) cho thấy sự thay đổi tương ứng ở output.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Belinkov, Y. (2022). Probing Classifiers: Promises, Shortcomings, and Alternatives. Computational Linguistics, 48(1), 207-219. https://arxiv.org/abs/2102.12492; Geiger, A., et al. (2021). Causal Abstractions of Neural Networks.</t>
         </is>
       </c>
     </row>
@@ -1004,10 +1029,15 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách câu hỏi `token nào?` khỏi câu hỏi `token ở vị trí nào?`.
-Phân tích theo nguyên lý thiết kế: Tách câu hỏi `token nào?` khỏi câu hỏi `token ở vị trí nào?`.</t>
+- Thông tin còn giữ lại (1.5 điểm): Nêu rõ token vẫn giữ thông tin bản sắc ngữ nghĩa từ điển độc lập (lexical embedding).
+- Thông tin bị mất đi (1.5 điểm): Nêu rõ mất hoàn toàn thông tin thứ tự trước sau, vị trí và cấu trúc tuần tự do tính chất hoán vị bất biến của attention.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Thông tin mỗi token VẪN CÓ: Bản sắc ngữ nghĩa từ vựng độc lập (lexical/semantic identity). Mỗi token vẫn giữ nguyên vector embedding từ vựng được tra cứu từ bảng từ điển (embedding lookup table), đại diện cho ý nghĩa trừu tượng cô lập của chính từ/ký tự đó trong không gian đặc trưng.
+- Thông tin BỊ THIẾU: Toàn bộ thông tin về vị trí tuyệt đối (absolute position), thứ tự tương đối trước sau (relative order), cũng như cấu trúc ngữ pháp tuần tự trong câu. Cơ chế Self-Attention nguyên bản là phép toán bất biến với phép hoán vị (permutation-invariant); nếu không có Positional Encoding, Transformer sẽ biến thành mô hình túi từ (Bag-of-Words) và không thể phân biệt được chủ ngữ, tân ngữ hay quan hệ bổ nghĩa khi đảo trật tự từ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Kiến trúc Transformer xử lý các phần tử đầu vào song song đồng thời (parallel processing), khác với RNN duyệt tuần tự. Do tính chất toán học của tích vô hướng ma trận Attention là hoán vị bất biến ($Attention(P X) = P Attention(X)$), tín hiệu vị trí (Positional Encoding / RoPE) là thành phần sống còn để mô hình nắm bắt cú pháp tuần tự của ngôn ngữ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Vaswani, A., et al. (2017). Attention Is All You Need. NeurIPS 2017. https://arxiv.org/abs/1706.03762; Su, J., et al. (2024). RoFormer: Enhanced Transformer with Rotary Position Embedding (RoPE).</t>
         </is>
       </c>
     </row>
@@ -1228,10 +1258,18 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mô tả cơ chế, không cần kết luận chắc chắn `nó` chỉ ai hoặc cái gì.
-Phân tích theo nguyên lý thiết kế: Mô tả cơ chế, không cần kết luận chắc chắn `nó` chỉ ai hoặc cái gì.</t>
+- Vai trò của Query (1.0 điểm): Mô tả đúng Q là nhu cầu truy vấn tìm kiếm thực thể tham chiếu phù hợp với ngữ cảnh 'dễ vỡ'.
+- Vai trò của Key (1.0 điểm): Mô tả đúng K là nhãn thuộc tính của các từ đứng trước để so khớp tương đồng qua tích vô hướng.
+- Vai trò của Value (1.0 điểm): Mô tả đúng V là nội dung ngữ nghĩa thực tế được trích xuất và hòa trộn vào biểu diễn mới của 'nó'.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Trong câu 'Lan đặt chiếc cốc lên bàn vì nó dễ vỡ', vai trò của Q, K, V khi token 'nó' thực hiện self-attention:
+- Query (Q) của 'nó': Đóng vai trò là câu hỏi hoặc yêu cầu tìm kiếm thông tin do chính 'nó' phát đi (Ví dụ: 'Tôi là đại từ thay thế, đối tượng nào đứng trước tôi có đặc tính tương thích với vị ngữ 'dễ vỡ'?').
+- Key (K) của các token đứng trước ('Lan', 'chiếc cốc', 'bàn'): Đóng vai trò là nhãn nhận diện hoặc hồ sơ thuộc tính để so khớp. Tích vô hướng giữa $Q_{nó}$ và $K_{chiếc\_cốc}$ sẽ cho điểm tương đồng cao nhất vì đặc tính vật lý 'dễ vỡ' phù hợp với 'chiếc cốc' hơn là 'Lan' hay 'bàn'.
+- Value (V) của các token: Chứa đựng nội dung thông tin biểu diễn ngữ nghĩa thực sự của đối tượng. Khi trọng số chú ý softmax giữa $Q_{nó}$ và $K_{chiếc\_cốc}$ đạt mức cao nhất, vector $V_{chiếc\_cốc}$ sẽ được truyền tải và hòa trộn vào vector biểu diễn trạng thái mới của token 'nó'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Cơ chế Scaled Dot-Product Attention hoạt động tương tự như một hệ thống truy vấn cơ sở dữ liệu mềm (soft database lookup): Query truy vấn qua các Key để tính trọng số tương đồng (Softmax Attention Weight), sau đó tính tổng có trọng số trên các Value để tổng hợp thông tin ngữ cảnh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Vaswani, A., et al. (2017). Attention Is All You Need. Section 3.2. https://arxiv.org/abs/1706.03762; Alammar, J. (2018). The Illustrated Transformer.</t>
         </is>
       </c>
     </row>
@@ -1265,10 +1303,26 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính hai tích vô hướng trước, rồi chia mỗi điểm cho √d_k. Sau softmax, dùng hai trọng số để nhân với V₁, V₂ rồi cộng theo từng chiều.
-Phân tích theo nguyên lý thiết kế: Tính hai tích vô hướng trước, rồi chia mỗi điểm cho √d_k. Sau softmax, dùng hai trọng số để nhân với V₁, V₂ rồi cộng theo từng chiều.</t>
+- Điểm sau chia tỷ lệ (1.0 điểm): Tính chính xác $S_1 = 1.000$ và $S_2 = 0.000$.
+- Trọng số softmax (1.0 điểm): Tính chính xác $w_1 \approx 0.731$ và $w_2 \approx 0.269$.
+- Vector đầu ra attention (1.0 điểm): Tính chính xác vector đầu ra $[0.731, 0.269]$.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thực hiện các bước tính toán Scaled Dot-Product Attention:
+1. Tính tích vô hướng và chia tỷ lệ ($d_k = 2 \Rightarrow \sqrt{d_k} = \sqrt{2}$):
+- $Q \cdot K_1 = [1, 0] \cdot [\sqrt{2}, 0] = 1 \times \sqrt{2} + 0 \times 0 = \sqrt{2}$.
+  Điểm sau chia tỷ lệ $S_1 = \frac{Q \cdot K_1}{\sqrt{d_k}} = \frac{\sqrt{2}}{\sqrt{2}} = 1.000$.
+- $Q \cdot K_2 = [1, 0] \cdot [0, 0] = 1 \times 0 + 0 \times 0 = 0$.
+  Điểm sau chia tỷ lệ $S_2 = \frac{Q \cdot K_2}{\sqrt{d_k}} = \frac{0}{\sqrt{2}} = 0.000$.
+2. Tính trọng số Softmax:
+- $e^{S_1} = e^{1} \approx 2.71828$; $e^{S_2} = e^{0} = 1.00000$. Tổng = $2.71828 + 1.00000 = 3.71828$.
+- $w_1 = \frac{2.71828}{3.71828} \approx 0.731$.
+- $w_2 = \frac{1.00000}{3.71828} \approx 0.269$.
+3. Tính đầu ra Attention ($w_1 V_1 + w_2 V_2$):
+- $Output = 0.731 \times [1, 0] + 0.269 \times [0, 1] = [0.731, 0] + [0, 0.269] = [0.731, 0.269]$.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Công thức chuẩn $Attention(Q, K, V) = \text{softmax}\left(\frac{Q K^T}{\sqrt{d_k}}\right) V$. Việc chia cho $\sqrt{d_k}$ giữ phương sai của tích vô hướng ở mức 1, ngăn chặn giá trị quá lớn đẩy softmax vào vùng gradient bão hòa (vanishing gradient).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Vaswani, A., et al. (2017). Attention Is All You Need. Section 3.2.1. https://arxiv.org/abs/1706.03762</t>
         </is>
       </c>
     </row>
@@ -1302,10 +1356,26 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ở đây √d_k = 2; sau khi có trọng số vẫn phải cộng có trọng số hai vector Value.
-Phân tích theo nguyên lý thiết kế: Ở đây √d_k = 2; sau khi có trọng số vẫn phải cộng có trọng số hai vector Value.</t>
+- Điểm sau chia tỷ lệ (1.0 điểm): Tính đúng $S_1 = 1.000$ và $S_2 = 0.500$ (với $\sqrt{d_k}=2$).
+- Trọng số softmax (1.0 điểm): Tính đúng $w_1 \approx 0.622$ và $w_2 \approx 0.378$.
+- Vector đầu ra attention (1.0 điểm): Tính đúng vector đầu ra $[1.245, 1.133]$ (làm tròn 3 chữ số).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thực hiện các bước tính toán Scaled Dot-Product Attention:
+1. Tính tích vô hướng và chia tỷ lệ ($d_k = 4 \Rightarrow \sqrt{d_k} = \sqrt{4} = 2$):
+- $Q \cdot K_1 = [1, 1] \cdot [2, 0] = 1 \times 2 + 1 \times 0 = 2$.
+  Điểm sau chia tỷ lệ $S_1 = \frac{Q \cdot K_1}{2} = \frac{2}{2} = 1.000$.
+- $Q \cdot K_2 = [1, 1] \cdot [0, 1] = 1 \times 0 + 1 \times 1 = 1$.
+  Điểm sau chia tỷ lệ $S_2 = \frac{Q \cdot K_2}{2} = \frac{1}{2} = 0.500$.
+2. Tính trọng số Softmax:
+- $e^{S_1} = e^{1} \approx 2.71828$; $e^{S_2} = e^{0.5} \approx 1.64872$. Tổng = $2.71828 + 1.64872 = 4.36700$.
+- $w_1 = \frac{2.71828}{4.36700} \approx 0.622$.
+- $w_2 = \frac{1.64872}{4.36700} \approx 0.378$.
+3. Tính đầu ra Attention ($w_1 V_1 + w_2 V_2$):
+- $Output = 0.62246 \times [2, 0] + 0.37754 \times [0, 3] = [1.245, 0] + [0, 1.133] = [1.245, 1.133]$.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Với $d_k=4$, hệ số chuẩn hóa $\sqrt{d_k}=2$. Đầu ra là tổ hợp lồi (convex combination) của các vector Value theo phân phối xác suất sinh ra bởi softmax, định hình chính xác không gian đặc trưng tổng hợp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Vaswani, A., et al. (2017). Attention Is All You Need. Section 3.2.1. https://arxiv.org/abs/1706.03762</t>
         </is>
       </c>
     </row>
@@ -1380,10 +1450,15 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Trả lời hai phần: trọng số lớn nhất là bao nhiêu và trọng số đó không tự chứng minh điều gì.
-Phân tích theo nguyên lý thiết kế: Trả lời hai phần: trọng số lớn nhất là bao nhiêu và trọng số đó không tự chứng minh điều gì.</t>
+- Xác định quan hệ mạnh nhất (1.5 điểm): Nêu đúng quan hệ giữa 'cô ấy' và 'Mai' với trọng số cao nhất 0,70.
+- Nêu giới hạn diễn giải bản chất (1.5 điểm): Giải thích rõ attention weight không tương đương với giải thích nhân quả (không phản ánh toàn bộ quyết định của mạng nơ-ron qua các tầng sau).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Quan hệ mạnh nhất: Quan hệ liên kết mạnh nhất là giữa đại từ 'cô ấy' và thực thể 'Mai' với trọng số chú ý áp đảo đạt 0,70 (chiếm 70% tổng phân phối attention của head này so với 0,20 tới Lan và 0,10 tới dấu chấm).
+- Một giới hạn của kết luận từ map này: Trọng số attention chỉ phản ánh sự kết hợp tuyến tính trung gian tại một head ở một tầng cụ thể, KHÔNG PHẢI là bằng chứng giải thích quan hệ nhân quả (Attention is not explanation). Ta không thể kết luận chắc chắn rằng toàn bộ mô hình thực sự quyết định 'cô ấy' chính là 'Mai' ở đầu ra cuối cùng, vì các phép biến đổi phi tuyến tính qua MLP/FFN, các head khác và các tầng sâu hơn có thể điều chỉnh hoặc ghi đè thông tin này.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Luận điểm 'Attention is not Explanation' trong cộng đồng NLP chỉ ra rằng biểu đồ nhiệt attention map không đồng nhất với cơ chế giải thích nhân quả đáng tin cậy. Các head khác nhau có thể tập trung vào dấu câu hoặc cú pháp ngẫu nhiên mà không trực tiếp định đoạt dự đoán của token tiếp theo.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jain, S., &amp; Wallace, B. C. (2019). Attention is not Explanation. NAACL 2019. https://arxiv.org/abs/1902.10186; Wiegreffe, S., &amp; Pinter, Y. (2019). Attention is not not Explanation. EMNLP 2019.</t>
         </is>
       </c>
     </row>
